--- a/vehiclesMyDesk.xlsx
+++ b/vehiclesMyDesk.xlsx
@@ -87,7 +87,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>OTOS</t>
+    <t>localization/odom</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -480,7 +480,7 @@
     <col min="3" max="3" width="23.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.58203125" customWidth="1"/>
     <col min="6" max="6" width="8.58203125" customWidth="1"/>
-    <col min="7" max="7" width="10.58203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20.25" bestFit="1" customWidth="1"/>
   </cols>
